--- a/Backend/Input/social_programs/Planillas programas sociales.xlsx
+++ b/Backend/Input/social_programs/Planillas programas sociales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28926"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ATMM/Programas sociales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17A65123-23D2-4C45-A064-DCEC6F4D96B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="14_{B8137F6A-EFFB-4132-B0CD-8A6753A2AC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A8B3CF7-F086-46CE-9FFF-740EA547825C}"/>
   <bookViews>
-    <workbookView xWindow="28950" yWindow="3315" windowWidth="15270" windowHeight="7785" activeTab="2" xr2:uid="{605468A5-0570-42AA-B423-9BA778D8FF22}"/>
+    <workbookView xWindow="20370" yWindow="-6510" windowWidth="29040" windowHeight="15840" xr2:uid="{605468A5-0570-42AA-B423-9BA778D8FF22}"/>
   </bookViews>
   <sheets>
     <sheet name="programas sociales" sheetId="1" r:id="rId1"/>
@@ -38,12 +38,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
   <si>
     <t>SUBSECRETARÍA/SERVICIO</t>
   </si>
   <si>
+    <t>NÚMERO DE PROGRAMAS DICIEMBRE 2025</t>
+  </si>
+  <si>
+    <t>Hitos del proceso</t>
+  </si>
+  <si>
+    <t>Hitos de proceso de evaluación Ex Ante</t>
+  </si>
+  <si>
     <t>Dirección de Educación Pública</t>
+  </si>
+  <si>
+    <t> qweqweqwewqe</t>
+  </si>
+  <si>
+    <t>qweqweqwe</t>
   </si>
   <si>
     <t>Junta Nacional de Auxilio Escolar y Becas</t>
@@ -146,16 +161,27 @@
 ejecución año t-1</t>
   </si>
   <si>
-    <t>Envío de orientaciones 
+    <t>Envío de orientaciones
 a contrapartes internas</t>
   </si>
   <si>
-    <t>Reporte en 
+    <t>Reporte en
 plataforma</t>
   </si>
   <si>
     <t>Evaluación
 MDSyF</t>
+  </si>
+  <si>
+    <t>Inicio Ex ante</t>
+  </si>
+  <si>
+    <t>Envío de
+lineamientos
+internos</t>
+  </si>
+  <si>
+    <t>Ingreso máximo ex ante</t>
   </si>
   <si>
     <t>Publicación
@@ -163,14 +189,6 @@
 de monitoreo</t>
   </si>
   <si>
-    <t>Inicio Ex ante</t>
-  </si>
-  <si>
-    <t>Envío de 
-lineamientos 
-internos</t>
-  </si>
-  <si>
     <t>Iteración 1</t>
   </si>
   <si>
@@ -185,25 +203,15 @@
   <si>
     <t>Cierre
 ex ante</t>
-  </si>
-  <si>
-    <t>NÚMERO DE PROGRAMAS 2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -213,19 +221,6 @@
       <b/>
       <sz val="14"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -246,8 +241,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,24 +288,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF002060"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF008080"/>
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor theme="7"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -330,69 +356,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="1"/>
       </left>
@@ -403,36 +366,6 @@
         <color theme="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -466,8 +399,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="1"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
@@ -479,15 +412,165 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -495,91 +578,102 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="7">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -596,35 +690,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
@@ -638,37 +703,33 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
+      <border>
         <top style="thin">
           <color theme="1"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
         <bottom style="thin">
           <color theme="1"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border>
-        <top style="thin">
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top style="medium">
           <color theme="1"/>
         </top>
+        <bottom style="medium">
+          <color theme="1"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -690,52 +751,14 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top style="medium">
-          <color theme="1"/>
-        </top>
-        <bottom style="medium">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FF002060"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color theme="1"/>
         </left>
@@ -760,10 +783,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2BACF66D-E51E-4803-89FE-16519B228CA3}" name="Tabla3" displayName="Tabla3" ref="A1:B7" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" totalsRowDxfId="5" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2BACF66D-E51E-4803-89FE-16519B228CA3}" name="Tabla3" displayName="Tabla3" ref="A1:B7" totalsRowShown="0" headerRowDxfId="6" totalsRowDxfId="5" headerRowBorderDxfId="3" tableBorderDxfId="4" totalsRowBorderDxfId="2">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{982D2809-D275-4DA7-B3EB-1036F5595418}" name="SUBSECRETARÍA/SERVICIO" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{F509353C-90AD-4C7A-B065-D3FA96717981}" name="NÚMERO DE PROGRAMAS 2025" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{982D2809-D275-4DA7-B3EB-1036F5595418}" name="SUBSECRETARÍA/SERVICIO" totalsRowDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{F509353C-90AD-4C7A-B065-D3FA96717981}" name="NÚMERO DE PROGRAMAS DICIEMBRE 2025" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1086,66 +1109,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC74EBBA-59B9-4B19-88E3-02FEA93AD57C}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.85546875" customWidth="1"/>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
+    <col min="4" max="4" width="43.42578125" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="36" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="37.5" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="D2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="53.25" customHeight="1">
+      <c r="A3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="14">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8">
+      <c r="D3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="33" customHeight="1">
+      <c r="A4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8">
+    <row r="5" spans="1:5" ht="30" customHeight="1">
+      <c r="A5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="14">
+        <v>31</v>
+      </c>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" ht="36.75" customHeight="1">
+      <c r="A6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="10">
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1">
+      <c r="A7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="16">
         <v>25</v>
       </c>
     </row>
@@ -1161,7 +1206,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F48D57E2-322E-4545-99B3-2BF144CCF36E}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
@@ -1170,267 +1215,267 @@
     <col min="5" max="5" width="63.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:6" ht="33" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="24" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B3" s="14">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="23.25" customHeight="1">
+      <c r="A4" s="12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16">
+      <c r="B4" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="14">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="24" customHeight="1">
+      <c r="A6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="16">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="24">
+      <c r="A9" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75">
+      <c r="A10" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" customHeight="1">
+      <c r="A11" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="20"/>
+    </row>
+    <row r="12" spans="1:6" ht="15" customHeight="1">
+      <c r="A12" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="20"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1">
+      <c r="A13" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="20"/>
+    </row>
+    <row r="14" spans="1:6" ht="15" customHeight="1">
+      <c r="A14" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="20"/>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1">
+      <c r="A15" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="20"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1">
+      <c r="A16" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="20"/>
+      <c r="E16" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="20"/>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1">
+      <c r="A17" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16">
+      <c r="D17" s="20"/>
+      <c r="E17" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="20"/>
+    </row>
+    <row r="18" spans="1:6" ht="15" customHeight="1">
+      <c r="A18" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="18">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="25"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="26"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="26"/>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="26"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="26"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26" t="s">
+      <c r="D18" s="20"/>
+      <c r="E18" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="26"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26" t="s">
+      <c r="F18" s="20"/>
+    </row>
+    <row r="19" spans="1:6" ht="15" customHeight="1">
+      <c r="A19" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="20"/>
+    </row>
+    <row r="20" spans="1:6" ht="15" customHeight="1">
+      <c r="A20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="26"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="26"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="26"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="26"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="26"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="20"/>
+      <c r="E20" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="20"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1">
+      <c r="A21" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="20"/>
+      <c r="E21" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="20"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1">
+      <c r="A22" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="20"/>
+      <c r="E22" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="26"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="26"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="26"/>
+      <c r="F22" s="20"/>
+    </row>
+    <row r="23" spans="1:6" ht="15" customHeight="1">
+      <c r="A23" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="43">
@@ -1484,192 +1529,206 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03910EC-52DE-4FD2-B183-F73675024717}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
+    <row r="1" spans="1:4" ht="36">
+      <c r="A1" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="38.25" customHeight="1">
+      <c r="A2" s="24">
         <v>45646</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="21">
+      <c r="B2" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="30">
         <v>2</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22">
-        <v>45294</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="21">
+    <row r="3" spans="1:4" ht="38.25" customHeight="1">
+      <c r="A3" s="26">
+        <v>45660</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="31">
         <v>-1</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
-        <v>45317</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="21">
+    <row r="4" spans="1:4" ht="45.75" customHeight="1">
+      <c r="A4" s="26">
+        <v>45683</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="31">
         <v>1.5</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22">
+    <row r="5" spans="1:4" ht="36" customHeight="1">
+      <c r="A5" s="26">
         <v>45677</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="21">
+      <c r="B5" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="31">
         <v>-1</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22">
-        <v>45748</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="21">
+    <row r="6" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A6" s="26">
+        <v>45783</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="31">
+        <v>2</v>
+      </c>
+      <c r="D6" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A7" s="26">
+        <v>45791</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="31">
+        <v>-1</v>
+      </c>
+      <c r="D7" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27" customHeight="1">
+      <c r="A8" s="26">
+        <v>45807</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="31">
+        <v>2</v>
+      </c>
+      <c r="D8" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="51" customHeight="1">
+      <c r="A9" s="26">
+        <v>45809</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="31">
+        <v>-1</v>
+      </c>
+      <c r="D9" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A10" s="26">
+        <v>45814</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="31">
         <v>1</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D10" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
-        <v>45796</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="21">
-        <v>2</v>
-      </c>
-      <c r="D7" s="21">
+    <row r="11" spans="1:4" ht="26.25" customHeight="1">
+      <c r="A11" s="26">
+        <v>45821</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="31">
+        <v>-1</v>
+      </c>
+      <c r="D11" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
-        <v>45432</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="21">
+    <row r="12" spans="1:4" ht="23.25" customHeight="1">
+      <c r="A12" s="26">
+        <v>45828</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="31">
         <v>1</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D12" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
-        <v>45435</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="21">
+    <row r="13" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A13" s="26">
+        <v>45835</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="31">
         <v>-1</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D13" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
-        <v>45442</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="21">
-        <v>-1</v>
-      </c>
-      <c r="D10" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
-        <v>45449</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="21">
-        <v>-1</v>
-      </c>
-      <c r="D11" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
-        <v>45456</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="21">
-        <v>-1</v>
-      </c>
-      <c r="D12" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="22">
-        <v>45463</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="21">
+    <row r="14" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A14" s="26">
+        <v>45840</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="31">
         <v>1</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D14" s="33">
         <v>0</v>
       </c>
     </row>
@@ -1679,6 +1738,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="22" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="99316247900046118e13a249c2e2a979">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="18ff31ee8df8f768b70ea272e17d0ebc" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -1942,61 +2022,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F954266-84C9-4620-8B9D-ABF4D9802B95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF324DBD-E5B2-4ED3-A4FD-22826FEC5766}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF324DBD-E5B2-4ED3-A4FD-22826FEC5766}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4240189B-A8AD-49BC-A380-EBB9341BD063}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4240189B-A8AD-49BC-A380-EBB9341BD063}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F954266-84C9-4620-8B9D-ABF4D9802B95}"/>
 </file>
--- a/Backend/Input/social_programs/Planillas programas sociales.xlsx
+++ b/Backend/Input/social_programs/Planillas programas sociales.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28926"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ATMM/Programas sociales/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="14_{B8137F6A-EFFB-4132-B0CD-8A6753A2AC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A8B3CF7-F086-46CE-9FFF-740EA547825C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E67025-6CD6-4AE8-B750-1FC4F965FF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-6510" windowWidth="29040" windowHeight="15840" xr2:uid="{605468A5-0570-42AA-B423-9BA778D8FF22}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{605468A5-0570-42AA-B423-9BA778D8FF22}"/>
   </bookViews>
   <sheets>
     <sheet name="programas sociales" sheetId="1" r:id="rId1"/>
-    <sheet name="Monitoreo y exantes" sheetId="2" r:id="rId2"/>
+    <sheet name="Monitoreo y exante" sheetId="2" r:id="rId2"/>
     <sheet name="datos_graficos" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -38,29 +38,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="64">
+  <si>
+    <t>TOTAL PROGRAMAS SOCIALES MINEDUC 2025</t>
+  </si>
   <si>
     <t>SUBSECRETARÍA/SERVICIO</t>
   </si>
   <si>
-    <t>NÚMERO DE PROGRAMAS DICIEMBRE 2025</t>
-  </si>
-  <si>
-    <t>Hitos del proceso</t>
-  </si>
-  <si>
-    <t>Hitos de proceso de evaluación Ex Ante</t>
+    <t>NÚMERO DE PROGRAMAS SOCIALES</t>
   </si>
   <si>
     <t>Dirección de Educación Pública</t>
   </si>
   <si>
-    <t> qweqweqwewqe</t>
-  </si>
-  <si>
-    <t>qweqweqwe</t>
-  </si>
-  <si>
     <t>Junta Nacional de Auxilio Escolar y Becas</t>
   </si>
   <si>
@@ -76,73 +67,121 @@
     <t>Subsecretaría Educación Superior</t>
   </si>
   <si>
+    <t>TOTAL DE PROGRAMAS SOCIALES MONITOREADOS 2024</t>
+  </si>
+  <si>
     <t>SUBSECRETARÍA / SERVICIO</t>
   </si>
   <si>
     <t>MONITOREO</t>
   </si>
   <si>
-    <t>RESULTADO EX ANTE 2023</t>
+    <t>PROGRAMAS QUE INGRESAN AL PROCESO DE EVALUACIÓN EX ANTE 2026</t>
   </si>
   <si>
     <t>PROGRAMA</t>
   </si>
   <si>
-    <t>CATEGORÍA</t>
-  </si>
-  <si>
-    <t>Beca de Apoyo a la Retención Escolar</t>
-  </si>
-  <si>
-    <t>RF</t>
-  </si>
-  <si>
-    <t>Programa Habilidades para la Vida III</t>
+    <t>ESTADO</t>
+  </si>
+  <si>
+    <t>Hogares y Residencias Estudiantiles (Hogares Insulares V Región)</t>
+  </si>
+  <si>
+    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 09/06</t>
+  </si>
+  <si>
+    <t>Beca Integración Territorial (Programa Especial Beca Art. 56 Ley N° 18.681)</t>
+  </si>
+  <si>
+    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 12/06</t>
+  </si>
+  <si>
+    <t>Beca Polimetales Arica</t>
   </si>
   <si>
     <t>Subsecretaría de Educación</t>
   </si>
   <si>
-    <t>Educación Rural</t>
-  </si>
-  <si>
-    <t>Fortalecimiento del aprendizaje del inglés</t>
-  </si>
-  <si>
-    <t>Subvención Escolar Regular</t>
+    <t>Programa de Bienestar Socioemocional y Educación Integral</t>
+  </si>
+  <si>
+    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 19/06</t>
+  </si>
+  <si>
+    <t>Subvención Gratuidad
+*Se ha definido iniciar el desarrollo de las nuevas fichas con los grupos correspondientes a Carrera Docente y Gratuidad, dada su importancia estructural dentro del sistema de subvenciones escolares. Ambas representan pilares centrales de las reformas educativas de los últimos años, al abordar dimensiones clave como la equidad en el acceso y la profesionalización del cuerpo docente. Además de su relevancia técnica y programática, estas subvenciones tienen un peso presupuestario significativo, ya que en conjunto representan aproximadamente el 70% del gasto total actualmente contenido en la ficha "Otras Subvenciones Escolares". Por tanto, su priorización permite avanzar en una primera etapa con los componentes de mayor impacto financiero y estratégico del sistema.</t>
+  </si>
+  <si>
+    <t>Carrera Docente
+*Se ha definido iniciar el desarrollo de las nuevas fichas con los grupos correspondientes a Carrera Docente y Gratuidad, dada su importancia estructural dentro del sistema de subvenciones escolares. Ambas representan pilares centrales de las reformas educativas de los últimos años, al abordar dimensiones clave como la equidad en el acceso y la profesionalización del cuerpo docente. Además de su relevancia técnica y programática, estas subvenciones tienen un peso presupuestario significativo, ya que en conjunto representan aproximadamente el 70% del gasto total actualmente contenido en la ficha "Otras Subvenciones Escolares". Por tanto, su priorización permite avanzar en una primera etapa con los componentes de mayor impacto financiero y estratégico del sistema.</t>
+  </si>
+  <si>
+    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 11/06</t>
   </si>
   <si>
     <t>Subsecretaría de Educación Parvularia</t>
   </si>
   <si>
-    <t>Jardines Infantiles y Sala Cuna modalidad No Convencional</t>
-  </si>
-  <si>
-    <t>Vacaciones en mi Jardín</t>
-  </si>
-  <si>
-    <t>BP</t>
+    <t>Fonoinfancia</t>
+  </si>
+  <si>
+    <t>Jardines Infantiles y Salas Cuna Modalidad Convencional
+*Ingresa para Reformulación programática En Ante 2026, debido a que se incorporará dentro de su diseño los programas "Programa de Extensión Horaria" y "Programa Vacaciones en mi Jardín"</t>
+  </si>
+  <si>
+    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 13/06</t>
   </si>
   <si>
     <t>Subsecretaría de Educación Superior</t>
   </si>
   <si>
-    <t>Plan de Fortalecimiento de Universidades</t>
-  </si>
-  <si>
-    <t>Beca Bicentenario</t>
-  </si>
-  <si>
-    <t>Red Maestro de Maestros</t>
-  </si>
-  <si>
-    <t>Subvención Pro-Retención</t>
-  </si>
-  <si>
-    <t>Programa Jardín Transitorio Estacional</t>
-  </si>
-  <si>
-    <t>Programa Alternativo de Atención al Párvulo</t>
+    <t>Beca Reparacióin</t>
+  </si>
+  <si>
+    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 05/06</t>
+  </si>
+  <si>
+    <t>Programa de Acompañamiento y Acceso Efectivo a la Educación Superior (PACE) (PATP ingresaría como parte de PACE)</t>
+  </si>
+  <si>
+    <t>En evaluación. Primer informe de evaluación recibido con calificación FI al 30/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programa Educativo Alternativo de Atención del Párvulo </t>
+  </si>
+  <si>
+    <t>Jardín Infantil Clásico de Administración Directa</t>
+  </si>
+  <si>
+    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 06/06</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Clásico de Administración VTF</t>
+  </si>
+  <si>
+    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 10/06</t>
+  </si>
+  <si>
+    <t>Infraestructura y equipamiento para la Educación Pública del siglo XXI (incluirá Contingencia para Mantención y Reparación de Infraestructura Escolar (Plan de Reactivación Educativa)</t>
+  </si>
+  <si>
+    <t>Fondo de Apoyo a la Educación Pública (incluirá Financiamiento de la Educación Pública (Fondo de Incentivo para la Gestión Administrativa de los SLEP)</t>
+  </si>
+  <si>
+    <t>Fondo para la Reactivación Educativa (Plan de Reactivación Educativa)</t>
+  </si>
+  <si>
+    <t>Leyenda:</t>
+  </si>
+  <si>
+    <t>RF:Recomendación Favorable</t>
+  </si>
+  <si>
+    <t>OT: Objetado Técnicamente</t>
+  </si>
+  <si>
+    <t>FI: Falta de Información</t>
   </si>
   <si>
     <t>FECHA</t>
@@ -165,12 +204,12 @@
 a contrapartes internas</t>
   </si>
   <si>
+    <t>Evaluación
+MDSyF</t>
+  </si>
+  <si>
     <t>Reporte en
 plataforma</t>
-  </si>
-  <si>
-    <t>Evaluación
-MDSyF</t>
   </si>
   <si>
     <t>Inicio Ex ante</t>
@@ -184,21 +223,21 @@
     <t>Ingreso máximo ex ante</t>
   </si>
   <si>
+    <t>Iteración 1</t>
+  </si>
+  <si>
+    <t>Iteración 2</t>
+  </si>
+  <si>
+    <t>Iteración 3</t>
+  </si>
+  <si>
+    <t>Iteración 4</t>
+  </si>
+  <si>
     <t>Publicación
 de informes
 de monitoreo</t>
-  </si>
-  <si>
-    <t>Iteración 1</t>
-  </si>
-  <si>
-    <t>Iteración 2</t>
-  </si>
-  <si>
-    <t>Iteración 3</t>
-  </si>
-  <si>
-    <t>Iteración 4</t>
   </si>
   <si>
     <t>Cierre
@@ -209,7 +248,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,35 +263,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -277,6 +287,34 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -328,19 +366,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -369,50 +394,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -489,30 +473,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -571,6 +531,84 @@
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -578,102 +616,123 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="10">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -691,6 +750,9 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
@@ -703,6 +765,9 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border>
         <top style="thin">
           <color theme="1"/>
@@ -710,10 +775,21 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
           <color theme="1"/>
-        </bottom>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color theme="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="1"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -733,21 +809,13 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
           <color theme="1"/>
-        </left>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color theme="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="1"/>
-        </horizontal>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -783,10 +851,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2BACF66D-E51E-4803-89FE-16519B228CA3}" name="Tabla3" displayName="Tabla3" ref="A1:B7" totalsRowShown="0" headerRowDxfId="6" totalsRowDxfId="5" headerRowBorderDxfId="3" tableBorderDxfId="4" totalsRowBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2BACF66D-E51E-4803-89FE-16519B228CA3}" name="Tabla3" displayName="Tabla3" ref="A2:B8" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" totalsRowDxfId="5" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="4">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{982D2809-D275-4DA7-B3EB-1036F5595418}" name="SUBSECRETARÍA/SERVICIO" totalsRowDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{F509353C-90AD-4C7A-B065-D3FA96717981}" name="NÚMERO DE PROGRAMAS DICIEMBRE 2025" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{982D2809-D275-4DA7-B3EB-1036F5595418}" name="SUBSECRETARÍA/SERVICIO" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{F509353C-90AD-4C7A-B065-D3FA96717981}" name="NÚMERO DE PROGRAMAS SOCIALES" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1109,92 +1177,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC74EBBA-59B9-4B19-88E3-02FEA93AD57C}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.85546875" customWidth="1"/>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="43.42578125" customWidth="1"/>
-    <col min="5" max="5" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="36" customHeight="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="35"/>
+    </row>
+    <row r="2" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="B3" s="22">
         <v>4</v>
       </c>
-      <c r="B2" s="13">
-        <v>2</v>
-      </c>
-      <c r="D2" s="8" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="23">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="B5" s="23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="53.25" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="B6" s="23">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="14">
-        <v>26</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="B7" s="23">
         <v>6</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="33" customHeight="1">
-      <c r="A4" s="12" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="14">
-        <v>31</v>
-      </c>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="1:5" ht="36.75" customHeight="1">
-      <c r="A6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="14">
-        <v>6</v>
-      </c>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="16">
+      <c r="B8" s="25">
         <v>25</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
@@ -1205,324 +1260,332 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F48D57E2-322E-4545-99B3-2BF144CCF36E}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="37.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="63.5703125" customWidth="1"/>
+    <col min="4" max="4" width="67.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="35"/>
+    </row>
+    <row r="2" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="26" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="24" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="D11" s="26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="14">
+      <c r="B12" s="36"/>
+      <c r="C12" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="36"/>
+      <c r="C13" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="36"/>
+      <c r="C15" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="36"/>
+      <c r="C16" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="36"/>
+      <c r="C17" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="36" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A4" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="14">
+      <c r="B18" s="36"/>
+      <c r="C18" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="36"/>
+      <c r="C19" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="36"/>
+      <c r="C21" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="36" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="26.25" customHeight="1">
-      <c r="A5" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="14">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1">
-      <c r="A6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="16">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="24">
-      <c r="A9" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75">
-      <c r="A10" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18" t="s">
+      <c r="B22" s="36"/>
+      <c r="C22" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="36"/>
+      <c r="C23" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="36"/>
+      <c r="C24" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="36"/>
+      <c r="C25" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="18"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A11" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="20"/>
-    </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1">
-      <c r="A12" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="20"/>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1">
-      <c r="A13" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="20"/>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1">
-      <c r="A14" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="20"/>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1">
-      <c r="A15" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="20"/>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1">
-      <c r="A16" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="20"/>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1">
-      <c r="A17" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="20"/>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1">
-      <c r="A18" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21" t="s">
+    </row>
+    <row r="26" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="37"/>
+      <c r="C26" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="20"/>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1">
-      <c r="A19" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="20"/>
-    </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1">
-      <c r="A20" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="20"/>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1">
-      <c r="A21" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="20"/>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1">
-      <c r="A22" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1">
-      <c r="A23" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="20"/>
+    </row>
+    <row r="27" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="32" t="s">
+        <v>46</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="19">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1530,209 +1593,212 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03910EC-52DE-4FD2-B183-F73675024717}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="36">
-      <c r="A1" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="38.25" customHeight="1">
-      <c r="A2" s="24">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17">
         <v>45646</v>
       </c>
-      <c r="B2" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="30">
+      <c r="B2" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="13">
         <v>2</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="38.25" customHeight="1">
-      <c r="A3" s="26">
+    <row r="3" spans="1:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18">
         <v>45660</v>
       </c>
-      <c r="B3" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="31">
+      <c r="B3" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="14">
         <v>-1</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45.75" customHeight="1">
-      <c r="A4" s="26">
+    <row r="4" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18">
+        <v>45677</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="14">
+        <v>1</v>
+      </c>
+      <c r="D4" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18">
         <v>45683</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="31">
-        <v>1.5</v>
-      </c>
-      <c r="D4" s="33">
+      <c r="B5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="14">
+        <v>-1</v>
+      </c>
+      <c r="D5" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="36" customHeight="1">
-      <c r="A5" s="26">
-        <v>45677</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="31">
+    <row r="6" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>45783</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="14">
+        <v>2</v>
+      </c>
+      <c r="D6" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18">
+        <v>45791</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="14">
         <v>-1</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D7" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A6" s="26">
-        <v>45783</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="31">
+    <row r="8" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18">
+        <v>45807</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="14">
         <v>2</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D8" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="61.5" customHeight="1">
-      <c r="A7" s="26">
-        <v>45791</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="31">
+    <row r="9" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18">
+        <v>45814</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="14">
         <v>-1</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D9" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="27" customHeight="1">
-      <c r="A8" s="26">
-        <v>45807</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="31">
+    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18">
+        <v>45821</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="14">
+        <v>1</v>
+      </c>
+      <c r="D10" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18">
+        <v>45828</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="14">
+        <v>-1</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18">
+        <v>45835</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="14">
+        <v>1</v>
+      </c>
+      <c r="D12" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18">
+        <v>45838</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="14">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18">
+        <v>45840</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="14">
         <v>2</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D14" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="51" customHeight="1">
-      <c r="A9" s="26">
-        <v>45809</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="31">
-        <v>-1</v>
-      </c>
-      <c r="D9" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A10" s="26">
-        <v>45814</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="31">
-        <v>1</v>
-      </c>
-      <c r="D10" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="26.25" customHeight="1">
-      <c r="A11" s="26">
-        <v>45821</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="31">
-        <v>-1</v>
-      </c>
-      <c r="D11" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="23.25" customHeight="1">
-      <c r="A12" s="26">
-        <v>45828</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="31">
-        <v>1</v>
-      </c>
-      <c r="D12" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A13" s="26">
-        <v>45835</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="31">
-        <v>-1</v>
-      </c>
-      <c r="D13" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="33.75" customHeight="1">
-      <c r="A14" s="26">
-        <v>45840</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="31">
-        <v>1</v>
-      </c>
-      <c r="D14" s="33">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
+    <sortCondition ref="A1:A14"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1750,15 +1816,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="22" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="99316247900046118e13a249c2e2a979">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="18ff31ee8df8f768b70ea272e17d0ebc" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -2022,14 +2079,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF324DBD-E5B2-4ED3-A4FD-22826FEC5766}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF324DBD-E5B2-4ED3-A4FD-22826FEC5766}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4240189B-A8AD-49BC-A380-EBB9341BD063}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F954266-84C9-4620-8B9D-ABF4D9802B95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F954266-84C9-4620-8B9D-ABF4D9802B95}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4240189B-A8AD-49BC-A380-EBB9341BD063}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>